--- a/output/東北地方_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/東北地方_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -447,11 +447,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
@@ -465,90 +465,111 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>対象: 青森県・岩手県・秋田県・宮城県・山形県・福島県（山形県は現存する赤十字病院なし）</t>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>都県</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>病院名</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>調査した公表データ件数</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>X線関連該当件数</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Excelファイル</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>都県</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>病院名</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>調査した公表データ件数</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>X線関連該当件数</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Excelファイル</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>青森県</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>八戸赤十字病院</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>八戸赤十字病院_随意契約_X線関連.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>青森県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>八戸赤十字病院</t>
+          <t>盛岡赤十字病院</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>八戸赤十字病院_随意契約_X線関連.xlsx</t>
+          <t>盛岡赤十字病院_随意契約_X線関連.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>岩手県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>盛岡赤十字病院</t>
+          <t>仙台赤十字病院</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>X線関連契約の該当なし</t>
+        </is>
+      </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>盛岡赤十字病院_随意契約_X線関連.xlsx</t>
+          <t>仙台赤十字病院_随意契約_X線関連.xlsx</t>
         </is>
       </c>
     </row>
@@ -560,112 +581,84 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>仙台赤十字病院</t>
+          <t>石巻赤十字病院</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>X線関連契約の該当なし</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr"/>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>仙台赤十字病院_随意契約_X線関連.xlsx</t>
+          <t>石巻赤十字病院_随意契約_X線関連.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>秋田県</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>石巻赤十字病院</t>
+          <t>秋田赤十字病院</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>公表データを確認できず（詳細はExcel参照）</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>石巻赤十字病院_随意契約_X線関連.xlsx</t>
+          <t>秋田赤十字病院_随意契約_X線関連.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>秋田県</t>
+          <t>福島県</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>秋田赤十字病院</t>
+          <t>福島赤十字病院</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>公表データを確認できず（詳細はExcel参照）</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>秋田赤十字病院_随意契約_X線関連.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>福島県</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>福島赤十字病院</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>27</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr"/>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
           <t>福島赤十字病院_随意契約_X線関連.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>152</v>
-      </c>
-      <c r="D12" s="4" t="n">
+      <c r="C11" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -684,7 +677,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>

--- a/output/東北地方_赤十字病院_随意契約_X線関連_サマリー.xlsx
+++ b/output/東北地方_赤十字病院_随意契約_X線関連_サマリー.xlsx
@@ -451,11 +451,11 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,7 +677,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
